--- a/artfynd/A 25992-2023 artfynd.xlsx
+++ b/artfynd/A 25992-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125234013</v>
       </c>
       <c r="B2" t="n">
-        <v>100279</v>
+        <v>100451</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 25992-2023 artfynd.xlsx
+++ b/artfynd/A 25992-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125234013</v>
       </c>
       <c r="B2" t="n">
-        <v>100506</v>
+        <v>100513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25992-2023 artfynd.xlsx
+++ b/artfynd/A 25992-2023 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>125876563</v>
       </c>
       <c r="B3" t="n">
-        <v>58186</v>
+        <v>58187</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 25992-2023 artfynd.xlsx
+++ b/artfynd/A 25992-2023 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>125876563</v>
       </c>
       <c r="B3" t="n">
-        <v>58187</v>
+        <v>58188</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 25992-2023 artfynd.xlsx
+++ b/artfynd/A 25992-2023 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>125876563</v>
       </c>
       <c r="B3" t="n">
-        <v>58188</v>
+        <v>58192</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 25992-2023 artfynd.xlsx
+++ b/artfynd/A 25992-2023 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>125876563</v>
       </c>
       <c r="B3" t="n">
-        <v>58192</v>
+        <v>58195</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 25992-2023 artfynd.xlsx
+++ b/artfynd/A 25992-2023 artfynd.xlsx
@@ -675,60 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125234013</v>
+        <v>125876563</v>
       </c>
       <c r="B2" t="n">
-        <v>100513</v>
+        <v>58497</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>102990</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hygge, Hls</t>
+          <t>Grådbäcken, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561043</v>
+        <v>561036</v>
       </c>
       <c r="R2" t="n">
-        <v>6850875</v>
+        <v>6850732</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,17 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På hygge</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,7 +758,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -790,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125876563</v>
+        <v>125234013</v>
       </c>
       <c r="B3" t="n">
-        <v>58195</v>
+        <v>101326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,41 +787,49 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102990</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Grådbäcken, Hls</t>
+          <t>Hygge, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561036</v>
+        <v>561043</v>
       </c>
       <c r="R3" t="n">
-        <v>6850732</v>
+        <v>6850875</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,12 +853,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På hygge</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -873,6 +872,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 25992-2023 artfynd.xlsx
+++ b/artfynd/A 25992-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125876563</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,8 +898,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125234013</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>